--- a/Matrice de tests.xlsx
+++ b/Matrice de tests.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/pr17bcu_eduvaud_ch/Documents/Pre-TPI_John_Jaccard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{E60F0E24-B159-4C1C-8BC0-0C93A5B3A297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0269C5A1-7F21-4E88-BB3C-B9089A492E2F}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="8_{E60F0E24-B159-4C1C-8BC0-0C93A5B3A297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C92D51C1-89DA-4884-AD38-6C2DBC34F130}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="345" yWindow="3195" windowWidth="21600" windowHeight="11295" xr2:uid="{175F8C55-D8DF-4770-9698-881CA507BF8C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{175F8C55-D8DF-4770-9698-881CA507BF8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Tableau2[#All]</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="51">
   <si>
     <t>Test de création d’un élève</t>
   </si>
@@ -132,6 +135,63 @@
   </si>
   <si>
     <t>Mettre un élève absent pour un cours</t>
+  </si>
+  <si>
+    <t>Christophe Fonseca</t>
+  </si>
+  <si>
+    <t>Validé</t>
+  </si>
+  <si>
+    <t>A pu voir le profil connecté</t>
+  </si>
+  <si>
+    <t>A pu voir les moyenne</t>
+  </si>
+  <si>
+    <t>A pu voir les absences</t>
+  </si>
+  <si>
+    <t>Fonctionnent</t>
+  </si>
+  <si>
+    <t>A vu le planning avec la classe</t>
+  </si>
+  <si>
+    <t>justificatif recu</t>
+  </si>
+  <si>
+    <t>Chaque élève a recu sa note</t>
+  </si>
+  <si>
+    <t>a fonctionné</t>
+  </si>
+  <si>
+    <t>Modifiée directement sans latence</t>
+  </si>
+  <si>
+    <t>Vu</t>
+  </si>
+  <si>
+    <t>Cours n'apparait plus</t>
+  </si>
+  <si>
+    <t>Cours apparait</t>
+  </si>
+  <si>
+    <t>Visible, même si manque d'explication sur boutons</t>
+  </si>
+  <si>
+    <t>Changement visible</t>
+  </si>
+  <si>
+    <t>bien supprimé</t>
+  </si>
+  <si>
+    <t>affiché directement</t>
+  </si>
+  <si>
+    <t>Fonctionne</t>
   </si>
 </sst>
 </file>
@@ -219,7 +279,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -301,17 +361,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -356,10 +405,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
@@ -367,23 +412,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Insatisfaisant" xfId="2" builtinId="27"/>
@@ -392,46 +453,6 @@
     <cellStyle name="Satisfaisant" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -455,145 +476,34 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -603,30 +513,8 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
+      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -664,26 +552,188 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -704,16 +754,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EA330308-C534-45AC-8F58-EC24E62FB585}" name="Tableau2" displayName="Tableau2" ref="A1:G21" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EA330308-C534-45AC-8F58-EC24E62FB585}" name="Tableau2" displayName="Tableau2" ref="A1:G21" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
   <autoFilter ref="A1:G21" xr:uid="{EA330308-C534-45AC-8F58-EC24E62FB585}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8EEE336A-3439-4D70-9372-4A68B43368CA}" name="Date du test" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{1FC2E324-9E6D-4801-8AA0-C9D444575A41}" name="Nom" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{4B405FA1-5BA5-4906-BA89-D1585A75C175}" name="Titre du test" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{7E25501B-9434-4147-A125-3E8EB7A7A3CF}" name="Écran" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{5B6ED8D9-0CE3-4474-9A48-CE12E448817E}" name="Type de droit" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{268DE6FD-6521-49B2-8514-AA41D19F7151}" name="Statut" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{1F6E53B2-D4EF-4F17-A46A-579239E12C6A}" name="Preuve du statut" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8EEE336A-3439-4D70-9372-4A68B43368CA}" name="Date du test" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{1FC2E324-9E6D-4801-8AA0-C9D444575A41}" name="Nom" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{4B405FA1-5BA5-4906-BA89-D1585A75C175}" name="Titre du test" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{7E25501B-9434-4147-A125-3E8EB7A7A3CF}" name="Écran" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{5B6ED8D9-0CE3-4474-9A48-CE12E448817E}" name="Type de droit" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{268DE6FD-6521-49B2-8514-AA41D19F7151}" name="Statut" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{1F6E53B2-D4EF-4F17-A46A-579239E12C6A}" name="Preuve du statut" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1042,340 +1092,500 @@
     <col min="1" max="1" width="15.140625" customWidth="1"/>
     <col min="2" max="5" width="30.28515625" customWidth="1"/>
     <col min="6" max="6" width="23.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" customWidth="1"/>
     <col min="9" max="9" width="16.28515625" customWidth="1"/>
     <col min="10" max="10" width="20.140625" customWidth="1"/>
     <col min="11" max="11" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="6"/>
+      <c r="K1" s="4"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="17"/>
-      <c r="I2" s="7"/>
+      <c r="F2" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="17"/>
+      <c r="F3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="17"/>
+      <c r="F4" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="17"/>
+      <c r="F5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
+      <c r="A6" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="17"/>
+      <c r="F6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5" t="s">
+      <c r="A7" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="17"/>
+      <c r="F7" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5" t="s">
+      <c r="A8" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="17"/>
+      <c r="F8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5" t="s">
+      <c r="A9" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="17"/>
-      <c r="K9" s="6"/>
+      <c r="F9" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5" t="s">
+      <c r="A10" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="17"/>
-      <c r="K10" s="8"/>
+      <c r="F10" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5" t="s">
+      <c r="A11" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="17"/>
-      <c r="K11" s="9"/>
-    </row>
-    <row r="12" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5" t="s">
+      <c r="F11" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="17"/>
-      <c r="K12" s="10"/>
+      <c r="F12" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5" t="s">
+      <c r="A13" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="17"/>
+      <c r="F13" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5" t="s">
+      <c r="A14" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="17"/>
+      <c r="F14" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5" t="s">
+      <c r="A15" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="17"/>
+      <c r="F15" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5" t="s">
+      <c r="A16" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="17"/>
+      <c r="F16" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5" t="s">
+      <c r="A17" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="17"/>
+      <c r="F17" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5" t="s">
+      <c r="A18" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="17"/>
+      <c r="F18" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5" t="s">
+      <c r="A19" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="17"/>
+      <c r="F19" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5" t="s">
+      <c r="A20" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="17"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15" t="s">
+      <c r="F20" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="16"/>
+      <c r="F21" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
@@ -1455,13 +1665,8 @@
       <c r="E37" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{66B2EE14-25BD-4F8B-92A8-09AADADD2E1A}">
-      <formula1>$K$10:$K$12</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
